--- a/public/plantilla-matriz-peligros.xlsx
+++ b/public/plantilla-matriz-peligros.xlsx
@@ -15,7 +15,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="41">
+  <numFmts count="0"/>
+  <fonts count="43">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -305,6 +306,15 @@
       <name val="Arial"/>
       <b val="1"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="20">
@@ -1033,7 +1043,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="366">
+  <cellXfs count="379">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
@@ -1955,6 +1965,50 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2729,20 +2783,20 @@
         </is>
       </c>
       <c r="B11" s="89" t="n"/>
-      <c r="C11" s="68" t="n"/>
-      <c r="D11" s="93" t="n"/>
-      <c r="E11" s="93" t="n"/>
-      <c r="F11" s="93" t="n"/>
-      <c r="G11" s="89" t="n"/>
+      <c r="C11" s="366" t="n"/>
+      <c r="D11" s="367" t="n"/>
+      <c r="E11" s="367" t="n"/>
+      <c r="F11" s="367" t="n"/>
+      <c r="G11" s="368" t="n"/>
       <c r="H11" s="59" t="inlineStr">
         <is>
           <t>Fecha de elaboración</t>
         </is>
       </c>
       <c r="I11" s="89" t="n"/>
-      <c r="J11" s="69" t="n"/>
-      <c r="K11" s="93" t="n"/>
-      <c r="L11" s="89" t="n"/>
+      <c r="J11" s="369" t="n"/>
+      <c r="K11" s="367" t="n"/>
+      <c r="L11" s="368" t="n"/>
       <c r="M11" s="59" t="inlineStr">
         <is>
           <t>Versión de la matriz</t>
@@ -2750,9 +2804,9 @@
       </c>
       <c r="N11" s="93" t="n"/>
       <c r="O11" s="89" t="n"/>
-      <c r="P11" s="69" t="n"/>
-      <c r="Q11" s="93" t="n"/>
-      <c r="R11" s="89" t="n"/>
+      <c r="P11" s="369" t="n"/>
+      <c r="Q11" s="367" t="n"/>
+      <c r="R11" s="368" t="n"/>
     </row>
     <row r="12" ht="19" customHeight="1" s="127">
       <c r="A12" s="59" t="inlineStr">
@@ -2761,20 +2815,20 @@
         </is>
       </c>
       <c r="B12" s="89" t="n"/>
-      <c r="C12" s="68" t="n"/>
-      <c r="D12" s="93" t="n"/>
-      <c r="E12" s="93" t="n"/>
-      <c r="F12" s="93" t="n"/>
-      <c r="G12" s="89" t="n"/>
+      <c r="C12" s="366" t="n"/>
+      <c r="D12" s="367" t="n"/>
+      <c r="E12" s="367" t="n"/>
+      <c r="F12" s="367" t="n"/>
+      <c r="G12" s="368" t="n"/>
       <c r="H12" s="59" t="inlineStr">
         <is>
           <t>Última actualización</t>
         </is>
       </c>
       <c r="I12" s="89" t="n"/>
-      <c r="J12" s="69" t="n"/>
-      <c r="K12" s="93" t="n"/>
-      <c r="L12" s="89" t="n"/>
+      <c r="J12" s="369" t="n"/>
+      <c r="K12" s="367" t="n"/>
+      <c r="L12" s="368" t="n"/>
       <c r="M12" s="59" t="inlineStr">
         <is>
           <t>Hoja N°</t>
@@ -2782,9 +2836,9 @@
       </c>
       <c r="N12" s="93" t="n"/>
       <c r="O12" s="89" t="n"/>
-      <c r="P12" s="69" t="n"/>
-      <c r="Q12" s="93" t="n"/>
-      <c r="R12" s="89" t="n"/>
+      <c r="P12" s="369" t="n"/>
+      <c r="Q12" s="367" t="n"/>
+      <c r="R12" s="368" t="n"/>
     </row>
     <row r="13" ht="19" customHeight="1" s="127">
       <c r="A13" s="59" t="inlineStr">
@@ -2793,18 +2847,18 @@
         </is>
       </c>
       <c r="B13" s="89" t="n"/>
-      <c r="C13" s="68" t="n"/>
-      <c r="D13" s="93" t="n"/>
-      <c r="E13" s="93" t="n"/>
-      <c r="F13" s="93" t="n"/>
-      <c r="G13" s="89" t="n"/>
+      <c r="C13" s="366" t="n"/>
+      <c r="D13" s="367" t="n"/>
+      <c r="E13" s="367" t="n"/>
+      <c r="F13" s="367" t="n"/>
+      <c r="G13" s="368" t="n"/>
       <c r="H13" s="59" t="inlineStr">
         <is>
           <t>Metodología</t>
         </is>
       </c>
       <c r="I13" s="89" t="n"/>
-      <c r="J13" s="69" t="inlineStr">
+      <c r="J13" s="370" t="inlineStr">
         <is>
           <t>GTC 45</t>
         </is>
@@ -2818,9 +2872,9 @@
       </c>
       <c r="N13" s="93" t="n"/>
       <c r="O13" s="89" t="n"/>
-      <c r="P13" s="68" t="n"/>
-      <c r="Q13" s="93" t="n"/>
-      <c r="R13" s="89" t="n"/>
+      <c r="P13" s="366" t="n"/>
+      <c r="Q13" s="367" t="n"/>
+      <c r="R13" s="368" t="n"/>
     </row>
     <row r="14" ht="16.5" customHeight="1" s="127">
       <c r="A14" s="137" t="inlineStr">
@@ -2939,448 +2993,448 @@
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" s="127">
-      <c r="A16" s="306" t="n">
+      <c r="A16" s="371" t="n">
         <v>1</v>
       </c>
-      <c r="B16" s="230" t="n"/>
-      <c r="C16" s="230" t="n"/>
-      <c r="D16" s="306" t="n"/>
-      <c r="E16" s="230" t="n"/>
-      <c r="F16" s="360" t="n"/>
-      <c r="G16" s="230" t="n"/>
-      <c r="H16" s="230" t="n"/>
-      <c r="I16" s="306" t="n"/>
-      <c r="J16" s="306" t="n"/>
-      <c r="K16" s="361">
+      <c r="B16" s="372" t="n"/>
+      <c r="C16" s="372" t="n"/>
+      <c r="D16" s="373" t="n"/>
+      <c r="E16" s="372" t="n"/>
+      <c r="F16" s="374" t="n"/>
+      <c r="G16" s="372" t="n"/>
+      <c r="H16" s="372" t="n"/>
+      <c r="I16" s="373" t="n"/>
+      <c r="J16" s="373" t="n"/>
+      <c r="K16" s="371">
         <f>IF(AND(I16&lt;&gt;"",J16&lt;&gt;""),I16*J16,"")</f>
         <v/>
       </c>
-      <c r="L16" s="361">
+      <c r="L16" s="371">
         <f>IF(K16="","",IF(K16&gt;=24,"Muy alto",IF(K16&gt;=10,"Alto",IF(K16&gt;=6,"Medio","Bajo"))))</f>
         <v/>
       </c>
-      <c r="M16" s="306" t="n"/>
-      <c r="N16" s="362">
+      <c r="M16" s="373" t="n"/>
+      <c r="N16" s="375">
         <f>IF(AND(K16&lt;&gt;"",M16&lt;&gt;""),K16*M16,"")</f>
         <v/>
       </c>
-      <c r="O16" s="362">
+      <c r="O16" s="375">
         <f>IF(N16="","",IF(N16&gt;=600,"I",IF(N16&gt;=150,"II",IF(N16&gt;=40,"III","IV"))))</f>
         <v/>
       </c>
-      <c r="P16" s="363">
+      <c r="P16" s="376">
         <f>IF(O16="","",IF(O16="I","No aceptable",IF(O16="II","No aceptable o aceptable con control específico",IF(O16="III","Mejorable","Aceptable"))))</f>
         <v/>
       </c>
-      <c r="Q16" s="306" t="n"/>
-      <c r="R16" s="230" t="n"/>
+      <c r="Q16" s="373" t="n"/>
+      <c r="R16" s="372" t="n"/>
     </row>
     <row r="17" ht="36" customHeight="1" s="127">
-      <c r="A17" s="306" t="n">
+      <c r="A17" s="371" t="n">
         <v>2</v>
       </c>
-      <c r="B17" s="230" t="n"/>
-      <c r="C17" s="230" t="n"/>
-      <c r="D17" s="306" t="n"/>
-      <c r="E17" s="230" t="n"/>
-      <c r="F17" s="360" t="n"/>
-      <c r="G17" s="230" t="n"/>
-      <c r="H17" s="230" t="n"/>
-      <c r="I17" s="306" t="n"/>
-      <c r="J17" s="306" t="n"/>
-      <c r="K17" s="361">
+      <c r="B17" s="372" t="n"/>
+      <c r="C17" s="372" t="n"/>
+      <c r="D17" s="373" t="n"/>
+      <c r="E17" s="372" t="n"/>
+      <c r="F17" s="374" t="n"/>
+      <c r="G17" s="372" t="n"/>
+      <c r="H17" s="372" t="n"/>
+      <c r="I17" s="373" t="n"/>
+      <c r="J17" s="373" t="n"/>
+      <c r="K17" s="371">
         <f>IF(AND(I17&lt;&gt;"",J17&lt;&gt;""),I17*J17,"")</f>
         <v/>
       </c>
-      <c r="L17" s="361">
+      <c r="L17" s="371">
         <f>IF(K17="","",IF(K17&gt;=24,"Muy alto",IF(K17&gt;=10,"Alto",IF(K17&gt;=6,"Medio","Bajo"))))</f>
         <v/>
       </c>
-      <c r="M17" s="306" t="n"/>
-      <c r="N17" s="362">
+      <c r="M17" s="373" t="n"/>
+      <c r="N17" s="375">
         <f>IF(AND(K17&lt;&gt;"",M17&lt;&gt;""),K17*M17,"")</f>
         <v/>
       </c>
-      <c r="O17" s="362">
+      <c r="O17" s="375">
         <f>IF(N17="","",IF(N17&gt;=600,"I",IF(N17&gt;=150,"II",IF(N17&gt;=40,"III","IV"))))</f>
         <v/>
       </c>
-      <c r="P17" s="363">
+      <c r="P17" s="376">
         <f>IF(O17="","",IF(O17="I","No aceptable",IF(O17="II","No aceptable o aceptable con control específico",IF(O17="III","Mejorable","Aceptable"))))</f>
         <v/>
       </c>
-      <c r="Q17" s="306" t="n"/>
-      <c r="R17" s="230" t="n"/>
+      <c r="Q17" s="373" t="n"/>
+      <c r="R17" s="372" t="n"/>
     </row>
     <row r="18" ht="36" customHeight="1" s="127">
-      <c r="A18" s="306" t="n">
+      <c r="A18" s="371" t="n">
         <v>3</v>
       </c>
-      <c r="B18" s="230" t="n"/>
-      <c r="C18" s="230" t="n"/>
-      <c r="D18" s="306" t="n"/>
-      <c r="E18" s="230" t="n"/>
-      <c r="F18" s="360" t="n"/>
-      <c r="G18" s="230" t="n"/>
-      <c r="H18" s="230" t="n"/>
-      <c r="I18" s="306" t="n"/>
-      <c r="J18" s="306" t="n"/>
-      <c r="K18" s="361">
+      <c r="B18" s="372" t="n"/>
+      <c r="C18" s="372" t="n"/>
+      <c r="D18" s="373" t="n"/>
+      <c r="E18" s="372" t="n"/>
+      <c r="F18" s="374" t="n"/>
+      <c r="G18" s="372" t="n"/>
+      <c r="H18" s="372" t="n"/>
+      <c r="I18" s="373" t="n"/>
+      <c r="J18" s="373" t="n"/>
+      <c r="K18" s="371">
         <f>IF(AND(I18&lt;&gt;"",J18&lt;&gt;""),I18*J18,"")</f>
         <v/>
       </c>
-      <c r="L18" s="361">
+      <c r="L18" s="371">
         <f>IF(K18="","",IF(K18&gt;=24,"Muy alto",IF(K18&gt;=10,"Alto",IF(K18&gt;=6,"Medio","Bajo"))))</f>
         <v/>
       </c>
-      <c r="M18" s="306" t="n"/>
-      <c r="N18" s="362">
+      <c r="M18" s="373" t="n"/>
+      <c r="N18" s="375">
         <f>IF(AND(K18&lt;&gt;"",M18&lt;&gt;""),K18*M18,"")</f>
         <v/>
       </c>
-      <c r="O18" s="362">
+      <c r="O18" s="375">
         <f>IF(N18="","",IF(N18&gt;=600,"I",IF(N18&gt;=150,"II",IF(N18&gt;=40,"III","IV"))))</f>
         <v/>
       </c>
-      <c r="P18" s="363">
+      <c r="P18" s="376">
         <f>IF(O18="","",IF(O18="I","No aceptable",IF(O18="II","No aceptable o aceptable con control específico",IF(O18="III","Mejorable","Aceptable"))))</f>
         <v/>
       </c>
-      <c r="Q18" s="306" t="n"/>
-      <c r="R18" s="230" t="n"/>
+      <c r="Q18" s="373" t="n"/>
+      <c r="R18" s="372" t="n"/>
     </row>
     <row r="19" ht="36" customHeight="1" s="127">
-      <c r="A19" s="306" t="n">
+      <c r="A19" s="371" t="n">
         <v>4</v>
       </c>
-      <c r="B19" s="230" t="n"/>
-      <c r="C19" s="230" t="n"/>
-      <c r="D19" s="306" t="n"/>
-      <c r="E19" s="230" t="n"/>
-      <c r="F19" s="360" t="n"/>
-      <c r="G19" s="230" t="n"/>
-      <c r="H19" s="230" t="n"/>
-      <c r="I19" s="306" t="n"/>
-      <c r="J19" s="306" t="n"/>
-      <c r="K19" s="361">
+      <c r="B19" s="372" t="n"/>
+      <c r="C19" s="372" t="n"/>
+      <c r="D19" s="373" t="n"/>
+      <c r="E19" s="372" t="n"/>
+      <c r="F19" s="374" t="n"/>
+      <c r="G19" s="372" t="n"/>
+      <c r="H19" s="372" t="n"/>
+      <c r="I19" s="373" t="n"/>
+      <c r="J19" s="373" t="n"/>
+      <c r="K19" s="371">
         <f>IF(AND(I19&lt;&gt;"",J19&lt;&gt;""),I19*J19,"")</f>
         <v/>
       </c>
-      <c r="L19" s="361">
+      <c r="L19" s="371">
         <f>IF(K19="","",IF(K19&gt;=24,"Muy alto",IF(K19&gt;=10,"Alto",IF(K19&gt;=6,"Medio","Bajo"))))</f>
         <v/>
       </c>
-      <c r="M19" s="306" t="n"/>
-      <c r="N19" s="362">
+      <c r="M19" s="373" t="n"/>
+      <c r="N19" s="375">
         <f>IF(AND(K19&lt;&gt;"",M19&lt;&gt;""),K19*M19,"")</f>
         <v/>
       </c>
-      <c r="O19" s="362">
+      <c r="O19" s="375">
         <f>IF(N19="","",IF(N19&gt;=600,"I",IF(N19&gt;=150,"II",IF(N19&gt;=40,"III","IV"))))</f>
         <v/>
       </c>
-      <c r="P19" s="363">
+      <c r="P19" s="376">
         <f>IF(O19="","",IF(O19="I","No aceptable",IF(O19="II","No aceptable o aceptable con control específico",IF(O19="III","Mejorable","Aceptable"))))</f>
         <v/>
       </c>
-      <c r="Q19" s="306" t="n"/>
-      <c r="R19" s="230" t="n"/>
+      <c r="Q19" s="373" t="n"/>
+      <c r="R19" s="372" t="n"/>
     </row>
     <row r="20" ht="36" customHeight="1" s="127">
-      <c r="A20" s="306" t="n">
+      <c r="A20" s="371" t="n">
         <v>5</v>
       </c>
-      <c r="B20" s="230" t="n"/>
-      <c r="C20" s="230" t="n"/>
-      <c r="D20" s="306" t="n"/>
-      <c r="E20" s="230" t="n"/>
-      <c r="F20" s="360" t="n"/>
-      <c r="G20" s="230" t="n"/>
-      <c r="H20" s="230" t="n"/>
-      <c r="I20" s="306" t="n"/>
-      <c r="J20" s="306" t="n"/>
-      <c r="K20" s="361">
+      <c r="B20" s="372" t="n"/>
+      <c r="C20" s="372" t="n"/>
+      <c r="D20" s="373" t="n"/>
+      <c r="E20" s="372" t="n"/>
+      <c r="F20" s="374" t="n"/>
+      <c r="G20" s="372" t="n"/>
+      <c r="H20" s="372" t="n"/>
+      <c r="I20" s="373" t="n"/>
+      <c r="J20" s="373" t="n"/>
+      <c r="K20" s="371">
         <f>IF(AND(I20&lt;&gt;"",J20&lt;&gt;""),I20*J20,"")</f>
         <v/>
       </c>
-      <c r="L20" s="361">
+      <c r="L20" s="371">
         <f>IF(K20="","",IF(K20&gt;=24,"Muy alto",IF(K20&gt;=10,"Alto",IF(K20&gt;=6,"Medio","Bajo"))))</f>
         <v/>
       </c>
-      <c r="M20" s="306" t="n"/>
-      <c r="N20" s="362">
+      <c r="M20" s="373" t="n"/>
+      <c r="N20" s="375">
         <f>IF(AND(K20&lt;&gt;"",M20&lt;&gt;""),K20*M20,"")</f>
         <v/>
       </c>
-      <c r="O20" s="362">
+      <c r="O20" s="375">
         <f>IF(N20="","",IF(N20&gt;=600,"I",IF(N20&gt;=150,"II",IF(N20&gt;=40,"III","IV"))))</f>
         <v/>
       </c>
-      <c r="P20" s="363">
+      <c r="P20" s="376">
         <f>IF(O20="","",IF(O20="I","No aceptable",IF(O20="II","No aceptable o aceptable con control específico",IF(O20="III","Mejorable","Aceptable"))))</f>
         <v/>
       </c>
-      <c r="Q20" s="306" t="n"/>
-      <c r="R20" s="230" t="n"/>
+      <c r="Q20" s="373" t="n"/>
+      <c r="R20" s="372" t="n"/>
     </row>
     <row r="21" ht="36" customHeight="1" s="127">
-      <c r="A21" s="306" t="n">
+      <c r="A21" s="371" t="n">
         <v>6</v>
       </c>
-      <c r="B21" s="230" t="n"/>
-      <c r="C21" s="230" t="n"/>
-      <c r="D21" s="306" t="n"/>
-      <c r="E21" s="230" t="n"/>
-      <c r="F21" s="360" t="n"/>
-      <c r="G21" s="230" t="n"/>
-      <c r="H21" s="230" t="n"/>
-      <c r="I21" s="306" t="n"/>
-      <c r="J21" s="306" t="n"/>
-      <c r="K21" s="361">
+      <c r="B21" s="372" t="n"/>
+      <c r="C21" s="372" t="n"/>
+      <c r="D21" s="373" t="n"/>
+      <c r="E21" s="372" t="n"/>
+      <c r="F21" s="374" t="n"/>
+      <c r="G21" s="372" t="n"/>
+      <c r="H21" s="372" t="n"/>
+      <c r="I21" s="373" t="n"/>
+      <c r="J21" s="373" t="n"/>
+      <c r="K21" s="371">
         <f>IF(AND(I21&lt;&gt;"",J21&lt;&gt;""),I21*J21,"")</f>
         <v/>
       </c>
-      <c r="L21" s="361">
+      <c r="L21" s="371">
         <f>IF(K21="","",IF(K21&gt;=24,"Muy alto",IF(K21&gt;=10,"Alto",IF(K21&gt;=6,"Medio","Bajo"))))</f>
         <v/>
       </c>
-      <c r="M21" s="306" t="n"/>
-      <c r="N21" s="362">
+      <c r="M21" s="373" t="n"/>
+      <c r="N21" s="375">
         <f>IF(AND(K21&lt;&gt;"",M21&lt;&gt;""),K21*M21,"")</f>
         <v/>
       </c>
-      <c r="O21" s="362">
+      <c r="O21" s="375">
         <f>IF(N21="","",IF(N21&gt;=600,"I",IF(N21&gt;=150,"II",IF(N21&gt;=40,"III","IV"))))</f>
         <v/>
       </c>
-      <c r="P21" s="363">
+      <c r="P21" s="376">
         <f>IF(O21="","",IF(O21="I","No aceptable",IF(O21="II","No aceptable o aceptable con control específico",IF(O21="III","Mejorable","Aceptable"))))</f>
         <v/>
       </c>
-      <c r="Q21" s="306" t="n"/>
-      <c r="R21" s="230" t="n"/>
+      <c r="Q21" s="373" t="n"/>
+      <c r="R21" s="372" t="n"/>
     </row>
     <row r="22" ht="36" customHeight="1" s="127">
-      <c r="A22" s="306" t="n">
+      <c r="A22" s="371" t="n">
         <v>7</v>
       </c>
-      <c r="B22" s="230" t="n"/>
-      <c r="C22" s="230" t="n"/>
-      <c r="D22" s="306" t="n"/>
-      <c r="E22" s="230" t="n"/>
-      <c r="F22" s="360" t="n"/>
-      <c r="G22" s="230" t="n"/>
-      <c r="H22" s="230" t="n"/>
-      <c r="I22" s="306" t="n"/>
-      <c r="J22" s="306" t="n"/>
-      <c r="K22" s="361">
+      <c r="B22" s="372" t="n"/>
+      <c r="C22" s="372" t="n"/>
+      <c r="D22" s="373" t="n"/>
+      <c r="E22" s="372" t="n"/>
+      <c r="F22" s="374" t="n"/>
+      <c r="G22" s="372" t="n"/>
+      <c r="H22" s="372" t="n"/>
+      <c r="I22" s="373" t="n"/>
+      <c r="J22" s="373" t="n"/>
+      <c r="K22" s="371">
         <f>IF(AND(I22&lt;&gt;"",J22&lt;&gt;""),I22*J22,"")</f>
         <v/>
       </c>
-      <c r="L22" s="361">
+      <c r="L22" s="371">
         <f>IF(K22="","",IF(K22&gt;=24,"Muy alto",IF(K22&gt;=10,"Alto",IF(K22&gt;=6,"Medio","Bajo"))))</f>
         <v/>
       </c>
-      <c r="M22" s="306" t="n"/>
-      <c r="N22" s="362">
+      <c r="M22" s="373" t="n"/>
+      <c r="N22" s="375">
         <f>IF(AND(K22&lt;&gt;"",M22&lt;&gt;""),K22*M22,"")</f>
         <v/>
       </c>
-      <c r="O22" s="362">
+      <c r="O22" s="375">
         <f>IF(N22="","",IF(N22&gt;=600,"I",IF(N22&gt;=150,"II",IF(N22&gt;=40,"III","IV"))))</f>
         <v/>
       </c>
-      <c r="P22" s="363">
+      <c r="P22" s="376">
         <f>IF(O22="","",IF(O22="I","No aceptable",IF(O22="II","No aceptable o aceptable con control específico",IF(O22="III","Mejorable","Aceptable"))))</f>
         <v/>
       </c>
-      <c r="Q22" s="306" t="n"/>
-      <c r="R22" s="230" t="n"/>
+      <c r="Q22" s="373" t="n"/>
+      <c r="R22" s="372" t="n"/>
     </row>
     <row r="23" ht="36" customHeight="1" s="127">
-      <c r="A23" s="306" t="n">
+      <c r="A23" s="371" t="n">
         <v>8</v>
       </c>
-      <c r="B23" s="230" t="n"/>
-      <c r="C23" s="230" t="n"/>
-      <c r="D23" s="306" t="n"/>
-      <c r="E23" s="230" t="n"/>
-      <c r="F23" s="360" t="n"/>
-      <c r="G23" s="230" t="n"/>
-      <c r="H23" s="230" t="n"/>
-      <c r="I23" s="306" t="n"/>
-      <c r="J23" s="306" t="n"/>
-      <c r="K23" s="361">
+      <c r="B23" s="372" t="n"/>
+      <c r="C23" s="372" t="n"/>
+      <c r="D23" s="373" t="n"/>
+      <c r="E23" s="372" t="n"/>
+      <c r="F23" s="374" t="n"/>
+      <c r="G23" s="372" t="n"/>
+      <c r="H23" s="372" t="n"/>
+      <c r="I23" s="373" t="n"/>
+      <c r="J23" s="373" t="n"/>
+      <c r="K23" s="371">
         <f>IF(AND(I23&lt;&gt;"",J23&lt;&gt;""),I23*J23,"")</f>
         <v/>
       </c>
-      <c r="L23" s="361">
+      <c r="L23" s="371">
         <f>IF(K23="","",IF(K23&gt;=24,"Muy alto",IF(K23&gt;=10,"Alto",IF(K23&gt;=6,"Medio","Bajo"))))</f>
         <v/>
       </c>
-      <c r="M23" s="306" t="n"/>
-      <c r="N23" s="362">
+      <c r="M23" s="373" t="n"/>
+      <c r="N23" s="375">
         <f>IF(AND(K23&lt;&gt;"",M23&lt;&gt;""),K23*M23,"")</f>
         <v/>
       </c>
-      <c r="O23" s="362">
+      <c r="O23" s="375">
         <f>IF(N23="","",IF(N23&gt;=600,"I",IF(N23&gt;=150,"II",IF(N23&gt;=40,"III","IV"))))</f>
         <v/>
       </c>
-      <c r="P23" s="363">
+      <c r="P23" s="376">
         <f>IF(O23="","",IF(O23="I","No aceptable",IF(O23="II","No aceptable o aceptable con control específico",IF(O23="III","Mejorable","Aceptable"))))</f>
         <v/>
       </c>
-      <c r="Q23" s="306" t="n"/>
-      <c r="R23" s="230" t="n"/>
+      <c r="Q23" s="373" t="n"/>
+      <c r="R23" s="372" t="n"/>
     </row>
     <row r="24" ht="36" customHeight="1" s="127">
-      <c r="A24" s="306" t="n">
+      <c r="A24" s="371" t="n">
         <v>9</v>
       </c>
-      <c r="B24" s="230" t="n"/>
-      <c r="C24" s="230" t="n"/>
-      <c r="D24" s="306" t="n"/>
-      <c r="E24" s="230" t="n"/>
-      <c r="F24" s="360" t="n"/>
-      <c r="G24" s="230" t="n"/>
-      <c r="H24" s="230" t="n"/>
-      <c r="I24" s="306" t="n"/>
-      <c r="J24" s="306" t="n"/>
-      <c r="K24" s="361">
+      <c r="B24" s="372" t="n"/>
+      <c r="C24" s="372" t="n"/>
+      <c r="D24" s="373" t="n"/>
+      <c r="E24" s="372" t="n"/>
+      <c r="F24" s="374" t="n"/>
+      <c r="G24" s="372" t="n"/>
+      <c r="H24" s="372" t="n"/>
+      <c r="I24" s="373" t="n"/>
+      <c r="J24" s="373" t="n"/>
+      <c r="K24" s="371">
         <f>IF(AND(I24&lt;&gt;"",J24&lt;&gt;""),I24*J24,"")</f>
         <v/>
       </c>
-      <c r="L24" s="361">
+      <c r="L24" s="371">
         <f>IF(K24="","",IF(K24&gt;=24,"Muy alto",IF(K24&gt;=10,"Alto",IF(K24&gt;=6,"Medio","Bajo"))))</f>
         <v/>
       </c>
-      <c r="M24" s="306" t="n"/>
-      <c r="N24" s="362">
+      <c r="M24" s="373" t="n"/>
+      <c r="N24" s="375">
         <f>IF(AND(K24&lt;&gt;"",M24&lt;&gt;""),K24*M24,"")</f>
         <v/>
       </c>
-      <c r="O24" s="362">
+      <c r="O24" s="375">
         <f>IF(N24="","",IF(N24&gt;=600,"I",IF(N24&gt;=150,"II",IF(N24&gt;=40,"III","IV"))))</f>
         <v/>
       </c>
-      <c r="P24" s="363">
+      <c r="P24" s="376">
         <f>IF(O24="","",IF(O24="I","No aceptable",IF(O24="II","No aceptable o aceptable con control específico",IF(O24="III","Mejorable","Aceptable"))))</f>
         <v/>
       </c>
-      <c r="Q24" s="306" t="n"/>
-      <c r="R24" s="230" t="n"/>
+      <c r="Q24" s="373" t="n"/>
+      <c r="R24" s="372" t="n"/>
     </row>
     <row r="25" ht="36" customHeight="1" s="127">
-      <c r="A25" s="306" t="n">
+      <c r="A25" s="371" t="n">
         <v>10</v>
       </c>
-      <c r="B25" s="230" t="n"/>
-      <c r="C25" s="230" t="n"/>
-      <c r="D25" s="306" t="n"/>
-      <c r="E25" s="230" t="n"/>
-      <c r="F25" s="360" t="n"/>
-      <c r="G25" s="230" t="n"/>
-      <c r="H25" s="230" t="n"/>
-      <c r="I25" s="306" t="n"/>
-      <c r="J25" s="306" t="n"/>
-      <c r="K25" s="361">
+      <c r="B25" s="372" t="n"/>
+      <c r="C25" s="372" t="n"/>
+      <c r="D25" s="373" t="n"/>
+      <c r="E25" s="372" t="n"/>
+      <c r="F25" s="374" t="n"/>
+      <c r="G25" s="372" t="n"/>
+      <c r="H25" s="372" t="n"/>
+      <c r="I25" s="373" t="n"/>
+      <c r="J25" s="373" t="n"/>
+      <c r="K25" s="371">
         <f>IF(AND(I25&lt;&gt;"",J25&lt;&gt;""),I25*J25,"")</f>
         <v/>
       </c>
-      <c r="L25" s="361">
+      <c r="L25" s="371">
         <f>IF(K25="","",IF(K25&gt;=24,"Muy alto",IF(K25&gt;=10,"Alto",IF(K25&gt;=6,"Medio","Bajo"))))</f>
         <v/>
       </c>
-      <c r="M25" s="306" t="n"/>
-      <c r="N25" s="362">
+      <c r="M25" s="373" t="n"/>
+      <c r="N25" s="375">
         <f>IF(AND(K25&lt;&gt;"",M25&lt;&gt;""),K25*M25,"")</f>
         <v/>
       </c>
-      <c r="O25" s="362">
+      <c r="O25" s="375">
         <f>IF(N25="","",IF(N25&gt;=600,"I",IF(N25&gt;=150,"II",IF(N25&gt;=40,"III","IV"))))</f>
         <v/>
       </c>
-      <c r="P25" s="363">
+      <c r="P25" s="376">
         <f>IF(O25="","",IF(O25="I","No aceptable",IF(O25="II","No aceptable o aceptable con control específico",IF(O25="III","Mejorable","Aceptable"))))</f>
         <v/>
       </c>
-      <c r="Q25" s="306" t="n"/>
-      <c r="R25" s="230" t="n"/>
+      <c r="Q25" s="373" t="n"/>
+      <c r="R25" s="372" t="n"/>
     </row>
     <row r="26" ht="36" customHeight="1" s="127">
-      <c r="A26" s="306" t="n">
+      <c r="A26" s="371" t="n">
         <v>11</v>
       </c>
-      <c r="B26" s="230" t="n"/>
-      <c r="C26" s="230" t="n"/>
-      <c r="D26" s="306" t="n"/>
-      <c r="E26" s="230" t="n"/>
-      <c r="F26" s="360" t="n"/>
-      <c r="G26" s="230" t="n"/>
-      <c r="H26" s="230" t="n"/>
-      <c r="I26" s="306" t="n"/>
-      <c r="J26" s="306" t="n"/>
-      <c r="K26" s="361">
+      <c r="B26" s="372" t="n"/>
+      <c r="C26" s="372" t="n"/>
+      <c r="D26" s="373" t="n"/>
+      <c r="E26" s="372" t="n"/>
+      <c r="F26" s="374" t="n"/>
+      <c r="G26" s="372" t="n"/>
+      <c r="H26" s="372" t="n"/>
+      <c r="I26" s="373" t="n"/>
+      <c r="J26" s="373" t="n"/>
+      <c r="K26" s="371">
         <f>IF(AND(I26&lt;&gt;"",J26&lt;&gt;""),I26*J26,"")</f>
         <v/>
       </c>
-      <c r="L26" s="361">
+      <c r="L26" s="371">
         <f>IF(K26="","",IF(K26&gt;=24,"Muy alto",IF(K26&gt;=10,"Alto",IF(K26&gt;=6,"Medio","Bajo"))))</f>
         <v/>
       </c>
-      <c r="M26" s="306" t="n"/>
-      <c r="N26" s="362">
+      <c r="M26" s="373" t="n"/>
+      <c r="N26" s="375">
         <f>IF(AND(K26&lt;&gt;"",M26&lt;&gt;""),K26*M26,"")</f>
         <v/>
       </c>
-      <c r="O26" s="362">
+      <c r="O26" s="375">
         <f>IF(N26="","",IF(N26&gt;=600,"I",IF(N26&gt;=150,"II",IF(N26&gt;=40,"III","IV"))))</f>
         <v/>
       </c>
-      <c r="P26" s="363">
+      <c r="P26" s="376">
         <f>IF(O26="","",IF(O26="I","No aceptable",IF(O26="II","No aceptable o aceptable con control específico",IF(O26="III","Mejorable","Aceptable"))))</f>
         <v/>
       </c>
-      <c r="Q26" s="306" t="n"/>
-      <c r="R26" s="230" t="n"/>
+      <c r="Q26" s="373" t="n"/>
+      <c r="R26" s="372" t="n"/>
     </row>
     <row r="27" ht="36" customHeight="1" s="127">
-      <c r="A27" s="306" t="n">
+      <c r="A27" s="371" t="n">
         <v>12</v>
       </c>
-      <c r="B27" s="230" t="n"/>
-      <c r="C27" s="230" t="n"/>
-      <c r="D27" s="306" t="n"/>
-      <c r="E27" s="230" t="n"/>
-      <c r="F27" s="360" t="n"/>
-      <c r="G27" s="230" t="n"/>
-      <c r="H27" s="230" t="n"/>
-      <c r="I27" s="306" t="n"/>
-      <c r="J27" s="306" t="n"/>
-      <c r="K27" s="361">
+      <c r="B27" s="372" t="n"/>
+      <c r="C27" s="372" t="n"/>
+      <c r="D27" s="373" t="n"/>
+      <c r="E27" s="372" t="n"/>
+      <c r="F27" s="374" t="n"/>
+      <c r="G27" s="372" t="n"/>
+      <c r="H27" s="372" t="n"/>
+      <c r="I27" s="373" t="n"/>
+      <c r="J27" s="373" t="n"/>
+      <c r="K27" s="371">
         <f>IF(AND(I27&lt;&gt;"",J27&lt;&gt;""),I27*J27,"")</f>
         <v/>
       </c>
-      <c r="L27" s="361">
+      <c r="L27" s="371">
         <f>IF(K27="","",IF(K27&gt;=24,"Muy alto",IF(K27&gt;=10,"Alto",IF(K27&gt;=6,"Medio","Bajo"))))</f>
         <v/>
       </c>
-      <c r="M27" s="306" t="n"/>
-      <c r="N27" s="362">
+      <c r="M27" s="373" t="n"/>
+      <c r="N27" s="375">
         <f>IF(AND(K27&lt;&gt;"",M27&lt;&gt;""),K27*M27,"")</f>
         <v/>
       </c>
-      <c r="O27" s="362">
+      <c r="O27" s="375">
         <f>IF(N27="","",IF(N27&gt;=600,"I",IF(N27&gt;=150,"II",IF(N27&gt;=40,"III","IV"))))</f>
         <v/>
       </c>
-      <c r="P27" s="363">
+      <c r="P27" s="376">
         <f>IF(O27="","",IF(O27="I","No aceptable",IF(O27="II","No aceptable o aceptable con control específico",IF(O27="III","Mejorable","Aceptable"))))</f>
         <v/>
       </c>
-      <c r="Q27" s="306" t="n"/>
-      <c r="R27" s="230" t="n"/>
+      <c r="Q27" s="373" t="n"/>
+      <c r="R27" s="372" t="n"/>
     </row>
     <row r="28" ht="16.5" customHeight="1" s="127">
       <c r="A28" s="137" t="inlineStr">
@@ -3565,30 +3619,30 @@
         </is>
       </c>
       <c r="B35" s="97" t="n"/>
-      <c r="C35" s="301" t="n"/>
-      <c r="D35" s="98" t="n"/>
-      <c r="E35" s="98" t="n"/>
-      <c r="F35" s="98" t="n"/>
-      <c r="G35" s="97" t="n"/>
+      <c r="C35" s="372" t="n"/>
+      <c r="D35" s="377" t="n"/>
+      <c r="E35" s="377" t="n"/>
+      <c r="F35" s="377" t="n"/>
+      <c r="G35" s="378" t="n"/>
       <c r="H35" s="302" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="I35" s="97" t="n"/>
-      <c r="J35" s="301" t="n"/>
-      <c r="K35" s="98" t="n"/>
-      <c r="L35" s="98" t="n"/>
-      <c r="M35" s="98" t="n"/>
-      <c r="N35" s="97" t="n"/>
+      <c r="J35" s="372" t="n"/>
+      <c r="K35" s="377" t="n"/>
+      <c r="L35" s="377" t="n"/>
+      <c r="M35" s="377" t="n"/>
+      <c r="N35" s="378" t="n"/>
       <c r="O35" s="302" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="P35" s="97" t="n"/>
-      <c r="Q35" s="301" t="n"/>
-      <c r="R35" s="97" t="n"/>
+      <c r="Q35" s="372" t="n"/>
+      <c r="R35" s="378" t="n"/>
     </row>
     <row r="36" ht="21" customHeight="1" s="127">
       <c r="A36" s="302" t="inlineStr">
@@ -3597,30 +3651,30 @@
         </is>
       </c>
       <c r="B36" s="97" t="n"/>
-      <c r="C36" s="301" t="n"/>
-      <c r="D36" s="98" t="n"/>
-      <c r="E36" s="98" t="n"/>
-      <c r="F36" s="98" t="n"/>
-      <c r="G36" s="97" t="n"/>
+      <c r="C36" s="372" t="n"/>
+      <c r="D36" s="377" t="n"/>
+      <c r="E36" s="377" t="n"/>
+      <c r="F36" s="377" t="n"/>
+      <c r="G36" s="378" t="n"/>
       <c r="H36" s="302" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="I36" s="97" t="n"/>
-      <c r="J36" s="301" t="n"/>
-      <c r="K36" s="98" t="n"/>
-      <c r="L36" s="98" t="n"/>
-      <c r="M36" s="98" t="n"/>
-      <c r="N36" s="97" t="n"/>
+      <c r="J36" s="372" t="n"/>
+      <c r="K36" s="377" t="n"/>
+      <c r="L36" s="377" t="n"/>
+      <c r="M36" s="377" t="n"/>
+      <c r="N36" s="378" t="n"/>
       <c r="O36" s="302" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="P36" s="97" t="n"/>
-      <c r="Q36" s="301" t="n"/>
-      <c r="R36" s="97" t="n"/>
+      <c r="Q36" s="372" t="n"/>
+      <c r="R36" s="378" t="n"/>
     </row>
     <row r="37" ht="21" customHeight="1" s="127">
       <c r="A37" s="302" t="inlineStr">
@@ -3629,30 +3683,30 @@
         </is>
       </c>
       <c r="B37" s="97" t="n"/>
-      <c r="C37" s="301" t="n"/>
-      <c r="D37" s="98" t="n"/>
-      <c r="E37" s="98" t="n"/>
-      <c r="F37" s="98" t="n"/>
-      <c r="G37" s="97" t="n"/>
+      <c r="C37" s="372" t="n"/>
+      <c r="D37" s="377" t="n"/>
+      <c r="E37" s="377" t="n"/>
+      <c r="F37" s="377" t="n"/>
+      <c r="G37" s="378" t="n"/>
       <c r="H37" s="302" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="I37" s="97" t="n"/>
-      <c r="J37" s="301" t="n"/>
-      <c r="K37" s="98" t="n"/>
-      <c r="L37" s="98" t="n"/>
-      <c r="M37" s="98" t="n"/>
-      <c r="N37" s="97" t="n"/>
+      <c r="J37" s="372" t="n"/>
+      <c r="K37" s="377" t="n"/>
+      <c r="L37" s="377" t="n"/>
+      <c r="M37" s="377" t="n"/>
+      <c r="N37" s="378" t="n"/>
       <c r="O37" s="302" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="P37" s="97" t="n"/>
-      <c r="Q37" s="301" t="n"/>
-      <c r="R37" s="97" t="n"/>
+      <c r="Q37" s="372" t="n"/>
+      <c r="R37" s="378" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="25" t="inlineStr">
@@ -3666,6 +3720,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="58">
     <mergeCell ref="M11:O11"/>
     <mergeCell ref="H35:I35"/>
